--- a/artfynd/A 7625-2026 artfynd.xlsx
+++ b/artfynd/A 7625-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131846509</v>
+        <v>134628338</v>
       </c>
       <c r="B2" t="n">
-        <v>104719</v>
+        <v>43472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220164</v>
+        <v>101242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alva Gudings 1:16 (2), Gtl</t>
+          <t>Alva Gudings, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700346</v>
+        <v>700363</v>
       </c>
       <c r="R2" t="n">
-        <v>6360078</v>
+        <v>6359889</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,31 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalkhäll, mindre, i öppen glänta i kalktallskog.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131846511</v>
+        <v>134628340</v>
       </c>
       <c r="B3" t="n">
-        <v>107598</v>
+        <v>43472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Alva Gudings 1:16 (2), Gtl</t>
+          <t>Alva Gudings, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700346</v>
+        <v>700339</v>
       </c>
       <c r="R3" t="n">
-        <v>6360078</v>
+        <v>6359842</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -842,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,31 +873,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkhäll, mindre, i öppen glänta i kalktallskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131846508</v>
+        <v>134628342</v>
       </c>
       <c r="B4" t="n">
-        <v>99858</v>
+        <v>43472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222309</v>
+        <v>101242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Alva Gudings 1:16 (2), Gtl</t>
+          <t>Alva Gudings, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700346</v>
+        <v>700326</v>
       </c>
       <c r="R4" t="n">
-        <v>6360078</v>
+        <v>6359850</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -944,17 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vårstarr kan inte uteslutas.</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -965,24 +980,2545 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkhäll, mindre, i öppen glänta i kalktallskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134628343</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>700313</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6359879</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134628344</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>700288</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6359904</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134628346</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>700325</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6359947</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134628347</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>700306</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6359998</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4 st fortplantningsområde</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134628348</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>700302</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6360016</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134628349</v>
+      </c>
+      <c r="B10" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>700299</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6360023</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134628350</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>700301</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6360021</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Större fortplantningsområde</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134629764</v>
+      </c>
+      <c r="B12" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>700361</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6359904</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Par och mycket bräken förökningsyta</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134629766</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>700346</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6359886</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2st vid förökningsyta med lundstarr bräken etc.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134629767</v>
+      </c>
+      <c r="B14" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>700363</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6359894</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2st flyger tillsammans</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134629768</v>
+      </c>
+      <c r="B15" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>700368</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6359899</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1st vid ytterligare förökningsyta med lundstarr och bräken fuktig mark höga träd som ger skydd.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134629769</v>
+      </c>
+      <c r="B16" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>700367</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6359904</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134629771</v>
+      </c>
+      <c r="B17" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>700351</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6359930</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 flög förbi</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134629772</v>
+      </c>
+      <c r="B18" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>700287</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6359943</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2st vid förökningsyta med lundstarr, bräken, höga träd som ändå släpper in solljus fläckvis, fuktigare mark i skugga.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134629773</v>
+      </c>
+      <c r="B19" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>700279</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6359966</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134629775</v>
+      </c>
+      <c r="B20" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>700265</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6360006</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134629776</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>700258</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6360002</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134629777</v>
+      </c>
+      <c r="B22" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>700256</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6359996</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134629779</v>
+      </c>
+      <c r="B23" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>700272</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6359978</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134629780</v>
+      </c>
+      <c r="B24" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Alva Gudings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>700347</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6359847</v>
+      </c>
+      <c r="S24" t="n">
+        <v>12</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>3st vid förökningsplats med lundstarr, bräken skugga i en sänka med undervegetation.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131846509</v>
+      </c>
+      <c r="B25" t="n">
+        <v>104719</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Alva Gudings 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>700346</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6360078</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkhäll, mindre, i öppen glänta i kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131846511</v>
+      </c>
+      <c r="B26" t="n">
+        <v>107598</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Alva Gudings 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>700346</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6360078</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkhäll, mindre, i öppen glänta i kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131846508</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99858</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Alva Gudings 1:16 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>700346</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6360078</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Alva</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Vårstarr kan inte uteslutas.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkhäll, mindre, i öppen glänta i kalktallskog.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7625-2026 artfynd.xlsx
+++ b/artfynd/A 7625-2026 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda  Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1860,12 +1860,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1972,12 +1972,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2084,12 +2084,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2196,12 +2196,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2308,12 +2308,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2420,12 +2420,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2532,12 +2532,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2639,12 +2639,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2751,12 +2751,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2863,12 +2863,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2975,12 +2975,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3087,12 +3087,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3199,12 +3199,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 7625-2026 artfynd.xlsx
+++ b/artfynd/A 7625-2026 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda  Svanberg , Margaret Rainey</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda  Svanberg , Margaret Rainey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda  Svanberg , Margaret Rainey</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda  Svanberg , Margaret Rainey</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda  Svanberg , Margaret Rainey</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda  Svanberg , Margaret Rainey</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda  Svanberg , Margaret Rainey</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda  Svanberg , Margaret Rainey</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda  Svanberg , Margaret Rainey</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna Helmersson, Esmeralda Svanberg, Margaret Rainey</t>
+          <t>Anna Helmersson, Esmeralda  Svanberg , Margaret Rainey</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1860,12 +1860,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1972,12 +1972,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2084,12 +2084,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2196,12 +2196,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2308,12 +2308,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2420,12 +2420,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2532,12 +2532,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2639,12 +2639,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2751,12 +2751,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2863,12 +2863,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2975,12 +2975,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3087,12 +3087,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3199,12 +3199,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 7625-2026 artfynd.xlsx
+++ b/artfynd/A 7625-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628338</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628340</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628342</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628343</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628344</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628346</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628347</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628348</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628349</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134628350</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629764</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1981,6 +2041,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629766</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629767</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629768</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629769</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629771</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2541,6 +2626,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629772</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2648,6 +2738,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629773</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2760,6 +2855,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629775</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2872,6 +2972,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629776</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2984,6 +3089,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629777</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3096,6 +3206,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629779</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3208,6 +3323,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134629780</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3310,6 +3430,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131846509</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3412,6 +3537,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131846511</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3519,8 +3649,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131846508</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>